--- a/z.说明文件/批量实验配置.xlsx
+++ b/z.说明文件/批量实验配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="6"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="实验组合" sheetId="1" r:id="rId1"/>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>minm</t>
     </r>
     <r>
@@ -470,6 +476,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>80</t>
     </r>
     <r>
@@ -496,6 +508,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>minc</t>
     </r>
     <r>
@@ -522,6 +540,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>minb</t>
     </r>
     <r>
@@ -548,6 +572,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>160</t>
     </r>
     <r>
@@ -580,6 +610,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">定义 SFC 请求的生成参数。按 </t>
     </r>
     <r>
@@ -603,6 +639,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>绘图时是否显示窗口（</t>
     </r>
     <r>
@@ -664,6 +706,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>maxbw</t>
     </r>
     <r>
@@ -688,6 +736,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>maxnr</t>
     </r>
     <r>
@@ -712,6 +766,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>裕量计算模式（</t>
     </r>
     <r>
@@ -749,6 +809,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>maxt</t>
     </r>
     <r>
@@ -773,6 +839,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>250</t>
     </r>
     <r>
@@ -815,6 +887,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="仿宋"/>
+        <charset val="134"/>
+      </rPr>
       <t>sortedRequests</t>
     </r>
     <r>
@@ -1024,11 +1101,6 @@
     </font>
     <font>
       <sz val="10.8"/>
-      <name val="var(--monospace)"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.8"/>
       <color rgb="FF333333"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
@@ -1037,6 +1109,11 @@
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.8"/>
+      <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1515,14 +1592,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1530,15 +1606,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3188,228 +3255,228 @@
       <c r="C2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
       <c r="G2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>3</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="5">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>3</v>
       </c>
     </row>
@@ -3420,152 +3487,152 @@
       <c r="C12" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="G12" s="6" t="s">
+      <c r="E12" s="3"/>
+      <c r="G12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" ht="15" spans="2:10">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="17" ht="15" spans="2:9">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>42</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:9">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="6" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3574,124 +3641,124 @@
         <v>146</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="G20" s="6" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="G20" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="21" ht="15" spans="2:9">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="G21" s="7" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="G21" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>1</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>100</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>5</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>800</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3702,111 +3769,111 @@
       <c r="C26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="4">
         <v>8</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>600</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>3</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>1.8</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:9">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>46236</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>12</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" ht="15" spans="2:9">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6">
         <v>46113</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:9">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="6" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3815,70 +3882,70 @@
         <v>167</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3889,52 +3956,52 @@
       <c r="C38" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="6">
         <v>1</v>
       </c>
     </row>

--- a/z.说明文件/批量实验配置.xlsx
+++ b/z.说明文件/批量实验配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="实验组合" sheetId="1" r:id="rId1"/>
@@ -1101,7 +1101,6 @@
     </font>
     <font>
       <sz val="10.8"/>
-      <color rgb="FF333333"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
@@ -1113,6 +1112,7 @@
     </font>
     <font>
       <sz val="10.8"/>
+      <color rgb="FF333333"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
